--- a/job-applications.xlsx
+++ b/job-applications.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Applied" sheetId="1" r:id="rId1"/>
-    <sheet name="Failed" sheetId="2" r:id="rId2"/>
-    <sheet name="Skipped" sheetId="3" r:id="rId3"/>
+    <sheet name="External" sheetId="2" r:id="rId2"/>
+    <sheet name="Failed" sheetId="3" r:id="rId3"/>
+    <sheet name="Skipped" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -399,15 +400,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I54"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -418,18 +421,24 @@
         <v>Date</v>
       </c>
       <c r="C1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="D1" t="str">
         <v>Job Title</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Company</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Location</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Apply URL</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>External URL</v>
+      </c>
+      <c r="I1" t="str">
         <v>Notes / Reason</v>
       </c>
     </row>
@@ -438,22 +447,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>25/4/2026, 4:10:58 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C2" t="str">
-        <v>Test Job</v>
+        <v>linkedin</v>
       </c>
       <c r="D2" t="str">
-        <v>Test Co</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>Hyderabad</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>https://example.com</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>test</v>
+        <v>https://jobs.pyjamahr.com/scoutinc/frontend-developer-167/apply?source=LINKEDIN</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="3">
@@ -461,22 +476,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>25/4/2026, 5:45:09 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C3" t="str">
-        <v>Backend Engineer</v>
+        <v>linkedin</v>
       </c>
       <c r="D3" t="str">
-        <v>Weekday AI (YC W21)</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>India (Remote)</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>https://apply.workable.com/weekday-1/j/03395B11CA/apply/</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Workable ATS - submitted successfully</v>
+        <v>https://jobs.lever.co/cprime/e5fd1d68-34c3-4120-b247-e6ac94c2c339/apply?lever-source=LinkedIn</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="4">
@@ -484,22 +505,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>25/4/2026, 5:54:20 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C4" t="str">
-        <v>Software Engineer (Fullstack, frontend-heavy), Product Trust</v>
+        <v>linkedin</v>
       </c>
       <c r="D4" t="str">
-        <v>Postman</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>Bengaluru, Karnataka, India</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>https://job-boards.greenhouse.io/postman/jobs/7704063003</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Greenhouse ATS - submitted successfully</v>
+        <v>https://apply.workable.com/weekday-1/j/03395B11CA</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="5">
@@ -507,22 +534,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>25/4/2026, 6:43:05 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C5" t="str">
-        <v>Frontend Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D5" t="str">
-        <v>Scoutit</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>Noida, UP</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>https://jobs.pyjamahr.com/scoutinc/frontend-developer-167/apply</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>Applied via pyjamahr ATS</v>
+        <v>https://jobs.pyjamahr.com/scoutinc/backend-software-engineer-5/apply?source=LINKEDIN</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="6">
@@ -530,22 +563,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>25/4/2026, 6:46:39 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C6" t="str">
-        <v>Front End Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D6" t="str">
-        <v>Cprime (INRY)</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>Hyderabad, India</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>https://jobs.lever.co/cprime/e5fd1d68-34c3-4120-b247-e6ac94c2c339/apply</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>Lever ATS; Drupal questions answered honestly with 0 exp</v>
+        <v>https://jobs.pyjamahr.com/scoutinc/full-stack-developer-53/apply?source=LINKEDIN</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="7">
@@ -553,22 +592,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>25/4/2026, 6:48:50 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C7" t="str">
-        <v>Backend Engineer</v>
+        <v>linkedin</v>
       </c>
       <c r="D7" t="str">
-        <v>Weekday AI (YC W21)</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>Remote, India</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>https://apply.workable.com/weekday-1/j/03395B11CA/apply/</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Workable ATS; submitted successfully</v>
+        <v>https://job-boards.greenhouse.io/postman/jobs/7704063003</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="8">
@@ -576,22 +621,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>25/4/2026, 6:51:56 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C8" t="str">
-        <v>Backend Software Engineer</v>
+        <v>linkedin</v>
       </c>
       <c r="D8" t="str">
-        <v>Scoutit</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>Noida, UP</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>https://jobs.pyjamahr.com/scoutinc/backend-software-engineer-5/apply</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>pyjamahr ATS; submitted successfully</v>
+        <v>https://adivi.ai/company/careers#application-form</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="9">
@@ -599,22 +650,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>25/4/2026, 6:53:28 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C9" t="str">
-        <v>Full Stack Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D9" t="str">
-        <v>Scoutit</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Pune, Maharashtra</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>https://jobs.pyjamahr.com/scoutinc/full-stack-developer-53/apply</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>pyjamahr ATS; submitted successfully</v>
+        <v>https://www.teknotentx.com/career/mern-stack-developer</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="10">
@@ -622,22 +679,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>25/4/2026, 6:59:35 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C10" t="str">
-        <v>Software Engineer (Fullstack, frontend-heavy), Product Trust</v>
+        <v>linkedin</v>
       </c>
       <c r="D10" t="str">
-        <v>Postman</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>Bengaluru, India</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>https://job-boards.greenhouse.io/postman/jobs/7704063003</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>Greenhouse ATS; submitted successfully</v>
+        <v>https://expinator.com/MERN-Stack-Developer</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Applied via Playwright automation</v>
       </c>
     </row>
     <row r="11">
@@ -645,22 +708,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>25/4/2026, 7:00:50 pm</v>
+        <v>26/4/2026, 12:14:47 pm</v>
       </c>
       <c r="C11" t="str">
-        <v>MERN Stack Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D11" t="str">
-        <v>ADIVI AI</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>Ahmedabad, Gujarat</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>https://adivi.ai/company/careers#application-form</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>Direct form; Application Sent confirmed</v>
+        <v>https://equip.co/job-posts/Y9oM6I/</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -668,22 +737,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>25/4/2026, 7:03:37 pm</v>
+        <v>26/4/2026, 12:23:41 pm</v>
       </c>
       <c r="C12" t="str">
-        <v>Mern stack Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D12" t="str">
-        <v>TeknotentX</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>Cannanore, Kerala</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>https://www.teknotentx.com/career/mern-stack-developer</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>Direct form submit; fields cleared after submit = success</v>
+        <v>https://jobs.lever.co/cprime/e5fd1d68-34c3-4120-b247-e6ac94c2c339/apply?lever-source=LinkedIn&amp;source=LinkedIn&amp;lever-source=LinkedInJobs&amp;lever-origin=applied&amp;lever-source%255B%255D=LinkedIn&amp;_pc=193155&amp;lever-source=LinkedInJobs</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -691,42 +766,1239 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>25/4/2026, 7:04:45 pm</v>
+        <v>26/4/2026, 12:25:27 pm</v>
       </c>
       <c r="C13" t="str">
-        <v>MERN Stack Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D13" t="str">
-        <v>Expinator Web Technology</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>Sahibzada Ajit Singh Nagar, Punjab</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>https://expinator.com/MERN-Stack-Developer</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Direct form; fields cleared after submit = success</v>
+        <v>https://apply.workable.com/j/03395B11CA</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>26/4/2026, 12:31:33 pm</v>
+      </c>
+      <c r="C14" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>https://www.careerprofile.epiroc.com/job/Bengaluru-Junior-Full-Stack-Developer-KA-560058/1365715833/?feedId=393633&amp;utm_source=LinkedInJobPostings</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>26/4/2026, 12:38:59 pm</v>
+      </c>
+      <c r="C15" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>https://ibqbjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/job/143983/?utm_medium=jobboard&amp;utm_source=linkedin</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>26/4/2026, 12:42:58 pm</v>
+      </c>
+      <c r="C16" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>https://www.dataix3.com/contact</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>26/4/2026, 12:48:31 pm</v>
+      </c>
+      <c r="C17" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>https://www.maxxzoomindia.in/career.html#apply</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>26/4/2026, 12:57:44 pm</v>
+      </c>
+      <c r="C18" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15162-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>26/4/2026, 12:58:43 pm</v>
+      </c>
+      <c r="C19" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15169-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>26/4/2026, 12:59:44 pm</v>
+      </c>
+      <c r="C20" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15170-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>26/4/2026, 1:18:04 pm</v>
+      </c>
+      <c r="C21" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>https://jobs.smartrecruiters.com/METROMAKRO/744000122746745-full-stack-engineer-java-react?trid=2d92f286-613b-4daf-9dfa-6340ffbecf73</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>26/4/2026, 1:21:15 pm</v>
+      </c>
+      <c r="C22" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>https://job-boards.greenhouse.io/bitgo/jobs/6209007002</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>26/4/2026, 7:22:00 pm</v>
+      </c>
+      <c r="C23" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>https://jobs.siemens.com/en_US/externaljobs/JobDetail/503612</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>26/4/2026, 7:40:29 pm</v>
+      </c>
+      <c r="C24" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>https://fa-etvl-saasfaprod1.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/job/141598/?utm_medium=jobboard&amp;utm_source=linkedIn</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>26/4/2026, 7:40:52 pm</v>
+      </c>
+      <c r="C25" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>https://www.instahyre.com/job-420391-frontend-engineer-at-emergent-bangalore/?utm_source=linkedin&amp;utm_medium=organic&amp;utm_campaign=linkedin_apply&amp;utm_term=420391</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>26/4/2026, 8:02:07 pm</v>
+      </c>
+      <c r="C26" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>https://walmart.wd5.myworkdayjobs.com/WalmartExternal/job/IN-KA-BANGALORE-Home-Office-PTPP2/Senior--Software-Engineer_R-2377942/apply?source=LinkedIn</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C27" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Tenacious Hr Solution</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-tenacious-hr-solution-hyderabad-bengaluru-delhi-ncr-2-to-5-years-270326014185</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C28" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Mondee</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-mondee-hyderabad-3-to-8-years-260326030193</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C29" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-cerebra-hyderabad-8-to-10-years-240426022134</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C30" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Full Stack Developer (Node.js + React)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Kapston Services</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-node-js-react-kapston-services-hyderabad-6-to-10-years-100426015767</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C31" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Full Stack Developer/Lead || Looking For Product based experience</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Valuelabs</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-lead-looking-for-product-based-experience-valuelabs-hyderabad-6-to-10-years-230426036038</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C32" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Gen AI(Full Stack) Developer Opening with CAPCO</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Capco</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>https://www.naukri.com/job-listings-gen-ai-full-stack-developer-opening-with-capco-capco-hyderabad-gurugram-bengaluru-7-to-12-years-250326020186</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C33" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Fullstack Developer - Agentic ai</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Recpoc Management Consultants</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-agentic-ai-recpoc-management-consultants-hyderabad-chennai-bengaluru-8-to-12-years-130426028404</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C34" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Technical Manager</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Intellisavvy</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>https://www.naukri.com/job-listings-technical-manager-intellisavvy-hyderabad-10-to-16-years-150426023972</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C35" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Full Stack Developer - AL &amp; ML</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Smartedge IT Services</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-al-ml-smartedge-it-services-hyderabad-5-to-10-years-020426025052</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C36" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Web Developer Fresher</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Turbomodus</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-fresher-turbomodus-hyderabad-0-to-0-years-250426010088</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C37" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D37" t="str">
+        <v>PixiJS Developer</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Confidential</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>https://www.naukri.com/job-listings-pixijs-developer-confidential-hyderabad-3-to-5-years-180426016948</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C38" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Data Scientist (MMM)</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Blend360 India</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>https://www.naukri.com/job-listings-data-scientist-mmm-blend360-india-hyderabad-4-to-8-years-230326010188</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C39" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Senior Data Scientist (GENAI)</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Blend360 India</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>https://www.naukri.com/job-listings-senior-data-scientist-genai-blend360-india-hyderabad-4-to-9-years-090426024216</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C40" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Senior ETL QA Analyst</v>
+      </c>
+      <c r="E40" t="str">
+        <v>ICE Data Services</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>https://www.naukri.com/job-listings-senior-etl-qa-analyst-ice-data-services-hyderabad-7-to-12-years-310326018649</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C41" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Sdet Engineer</v>
+      </c>
+      <c r="E41" t="str">
+        <v>ICE Data Services</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>https://www.naukri.com/job-listings-sdet-engineer-ice-data-services-hyderabad-7-to-12-years-310326018166</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C42" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Senior Data Engineer</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Callaway Digital Technologies</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>https://www.naukri.com/job-listings-senior-data-engineer-callaway-digital-technologies-hyderabad-7-to-10-years-060426009972</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C43" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Senior Ms Sql Server Database Administrator - Urgent</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Confidencial</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>https://www.naukri.com/job-listings-senior-ms-sql-server-database-administrator-urgent-confidencial-hyderabad-6-to-8-years-030426022211</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C44" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Senior Power Bi Developer</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Techinduct</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>https://www.naukri.com/job-listings-senior-power-bi-developer-tech-induct-services-hyderabad-7-to-12-years-020426007821</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C45" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Node.JS + React JS - Senior Full-Stack Developer</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>https://www.naukri.com/job-listings-node-js-react-js-senior-full-stack-developer-tata-consultancy-services-hyderabad-pune-chennai-5-to-10-years-170326033715</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C46" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Full Stack Developer - React JS, Node JS &amp; Python</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Deloitte Consulting</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-react-js-node-js-python-deloitte-consulting-hyderabad-bengaluru-6-to-9-years-260226031791</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C47" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Senior Software Engineer-Fullstack Developer</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Phenom People</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-fullstack-developer-phenom-people-hyderabad-3-to-4-years-020426020654</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C48" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Senior Java Script Developer - BFSI domain x4</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Spectrum Consulting</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-script-developer-bfsi-domain-x4-spectrum-consulting-hyderabad-bengaluru-dubai-5-to-10-years-240426024893</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C49" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Gulf: Senior Java Fullstack Developer</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Spectrum Consulting</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>https://www.naukri.com/job-listings-gulf-senior-java-fullstack-developer-spectrum-consulting-hyderabad-pune-bengaluru-5-to-8-years-240426024051</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C50" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Angular+NodeJS Developer</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Kiash Solutions LLP</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>https://www.naukri.com/job-listings-angular-nodejs-developer-kiash-solution-hyderabad-chennai-bengaluru-5-to-10-years-020426034867</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C51" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Senior Quality Analyst</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Softify Technologies</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>https://www.naukri.com/job-listings-senior-quality-analyst-softify-technologies-hyderabad-7-to-11-years-240426030005</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C52" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Database Developer</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Contenterra Software</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>https://www.naukri.com/job-listings-database-developer-contenterra-software-hyderabad-5-to-10-years-160226014383</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C53" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Senior Fullstack Software Engineer</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Alter Domus</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>https://www.naukri.com/job-listings-senior-fullstack-software-engineer-alter-domus-hyderabad-5-to-8-years-240426025472</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>Naukri quick-apply (prior run)</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>27/4/2026, 2:03:01 pm</v>
+      </c>
+      <c r="C54" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Blueapplecloud Technologies</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Hyderabad(Madhapur)</v>
+      </c>
+      <c r="G54" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-blueapplecloud-technologies-hyderabad-0-to-4-years-270426007135</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>Naukri quick-apply (auto)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I54"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I161"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -737,18 +2009,24 @@
         <v>Date</v>
       </c>
       <c r="C1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="D1" t="str">
         <v>Job Title</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Company</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Location</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Apply URL</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>External URL</v>
+      </c>
+      <c r="I1" t="str">
         <v>Notes / Reason</v>
       </c>
     </row>
@@ -757,22 +2035,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>25/4/2026, 4:10:58 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C2" t="str">
-        <v>Failed Job</v>
+        <v>naukri</v>
       </c>
       <c r="D2" t="str">
-        <v>Fail Co</v>
+        <v>Full Stack Developer</v>
       </c>
       <c r="E2" t="str">
-        <v>Bengaluru</v>
+        <v>Ratnam Solutions</v>
       </c>
       <c r="F2" t="str">
-        <v>https://fail.com</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>requires SSN</v>
+        <v>https://www.naukri.com/job-listings-full-stack-developer-ratnam-solutions-private-limited-hyderabad-2-to-7-years-220426501349</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="3">
@@ -780,22 +2064,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>25/4/2026, 5:55:15 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C3" t="str">
-        <v>Remote Full-Stack Developer</v>
+        <v>naukri</v>
       </c>
       <c r="D3" t="str">
-        <v>Turing</v>
+        <v>Full Stack Developer</v>
       </c>
       <c r="E3" t="str">
-        <v>India (Remote)</v>
+        <v>Onebridge Infotech</v>
       </c>
       <c r="F3" t="str">
-        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Requires Google sign-in + developer vetting process - not a direct apply</v>
+        <v>https://www.naukri.com/job-listings-full-stack-developer-onebridge-infotech-pvt-ltd-hyderabad-2-to-5-years-170426501442</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="4">
@@ -803,22 +2093,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>25/4/2026, 6:43:46 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C4" t="str">
-        <v>Frontend Developer I (React,TypeScript)</v>
+        <v>naukri</v>
       </c>
       <c r="D4" t="str">
-        <v>Quartic (quartic.ai)</v>
+        <v>Full Stack Developer</v>
       </c>
       <c r="E4" t="str">
-        <v>Remote</v>
+        <v>Ipropal</v>
       </c>
       <c r="F4" t="str">
-        <v>https://equip.co/job-posts/Y9oM6I/</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>equip.co requires email magic-link login — cannot automate</v>
+        <v>https://www.naukri.com/job-listings-full-stack-developer-ipropal-allps-hyderabad-2-to-6-years-150426501799</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="5">
@@ -826,22 +2122,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>25/4/2026, 6:44:50 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C5" t="str">
-        <v>Full Stack Software Engineer</v>
+        <v>naukri</v>
       </c>
       <c r="D5" t="str">
-        <v>SLB</v>
+        <v>Custom Software Engineer</v>
       </c>
       <c r="E5" t="str">
-        <v>Pune, India</v>
+        <v>Accenture</v>
       </c>
       <c r="F5" t="str">
-        <v>https://careers.slb.com/jobdescription.aspx?id=EF15161-en_US+1</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>SLB ATS requires account creation with email verification — cannot automate</v>
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-7-years-240426916000</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="6">
@@ -849,22 +2151,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>25/4/2026, 6:50:23 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C6" t="str">
-        <v>Junior Full Stack Developer</v>
+        <v>naukri</v>
       </c>
       <c r="D6" t="str">
-        <v>Epiroc Mining India Ltd</v>
+        <v>Custom Software Engineer</v>
       </c>
       <c r="E6" t="str">
-        <v>Bengaluru, India</v>
+        <v>Accenture</v>
       </c>
       <c r="F6" t="str">
-        <v>https://www.careerprofile.epiroc.com/job/Bengaluru-Junior-Full-Stack-Developer-KA-560058/1365715833/</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>SAP SuccessFactors ATS requires account login — cannot automate</v>
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-7-years-240426915889</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="7">
@@ -872,22 +2180,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>25/4/2026, 7:05:52 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C7" t="str">
-        <v>Software Engr II</v>
+        <v>naukri</v>
       </c>
       <c r="D7" t="str">
-        <v>Honeywell</v>
+        <v>Full Stack Software Engineer</v>
       </c>
       <c r="E7" t="str">
-        <v>Bengaluru, India</v>
+        <v>Amgen Inc</v>
       </c>
       <c r="F7" t="str">
-        <v>https://ibqbjb.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/job/143983/</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Oracle HCM ATS requires account creation with email verification — cannot automate</v>
+        <v>https://www.naukri.com/job-listings-full-stack-software-engineer-amgen-inc-hyderabad-2-to-6-years-210426927427</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>External — needs manual apply</v>
       </c>
     </row>
     <row r="8">
@@ -895,42 +2209,4487 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>25/4/2026, 7:05:52 pm</v>
+        <v>27/4/2026, 2:02:20 pm</v>
       </c>
       <c r="C8" t="str">
-        <v>DE - React Senior Developer - GDSF02</v>
+        <v>naukri</v>
       </c>
       <c r="D8" t="str">
-        <v>EY</v>
+        <v>Software Development Engineer</v>
       </c>
       <c r="E8" t="str">
-        <v>Gurugram, Haryana</v>
+        <v>Accenture</v>
       </c>
       <c r="F8" t="str">
-        <v>https://careers.ey.com/ey/job/Gurgaon-DE-React-Senior-Developer-GDSF02-HR-122010/1277970701/</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>EY careers portal requires account login — cannot automate; also Senior level role</v>
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-210426919688</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C9" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426918234</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C10" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426918229</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C11" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426917751</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C12" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426916999</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C13" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-210426916727</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C14" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-210426916725</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C15" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-210426916710</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C16" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-210426916620</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C17" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426916391</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C18" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426916387</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C19" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426916250</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C20" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Hawk Sense Business Solutions</v>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-hawk-sense-business-solutions-hyderabad-2-to-5-years-130126505709</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C21" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Oratrics: The Personality School</v>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-oratrics-the-personality-enrichment-school-hyderabad-3-to-6-years-110226504222</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C22" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Full-Stack Developer</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Aksvin Technologies</v>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-aksvin-technologies-hyderabad-3-to-8-years-031025502814</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C23" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Full Stack Developer (React &amp; Node JD)</v>
+      </c>
+      <c r="E23" t="str">
+        <v>Vertiscript Global It Services</v>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-react-node-jd-vertiscript-global-it-solution-hyderabad-3-to-6-years-031225502948</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C24" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Full Stack Developer - , - JPMC</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Photon</v>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-jpmc-photon-infotech-p-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-4-years-260425502132</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C25" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Tealvue Software Solutions</v>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-tealvue-software-solutions-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-4-years-111224501969</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C26" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Full Stack Developer, eCommerce</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Prayag Health</v>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-ecommerce-prayag-health-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-1-to-5-years-210121501377</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C27" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Aliqan Services</v>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-aliqan-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-6-years-091123501143</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C28" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D28" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Vimerse Infotech</v>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-vimerse-infotech-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-9-years-041024503248</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C29" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D29" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E29" t="str">
+        <v>TM Systems</v>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-tm-systems-pvt-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-5-years-010426505699</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C30" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D30" t="str">
+        <v>Full Stack Developer (Mid-Level)</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Datamaze Solutions</v>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-mid-level-datamaze-solutions-hyderabad-3-to-5-years-200126507405</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C31" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D31" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Ghrian Technologies</v>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-ghrian-technologies-pvt-ltd-hyderabad-3-to-4-years-010719500888</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C32" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E32" t="str">
+        <v>SEDOTS Info Technologies (P) Ltd</v>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-sedots-info-technologies-p-ltd-hyderabad-0-to-1-years-090426500281</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C33" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D33" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Divami Design Labs</v>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-divami-hyderabad-3-to-7-years-151025504097</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C34" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D34" t="str">
+        <v>Full stack Developer -</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Tech Stalwart Solution</v>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-tech-stalwart-solution-private-limited-hyderabad-2-to-7-years-100325501440</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C35" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D35" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Pipra Solutions</v>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-pipra-solutions-pvt-ltd-hyderabad-3-to-8-years-241225501410</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C36" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D36" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Salientminds Technologies</v>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-salientminds-technologies-private-limited-hyderabad-2-to-6-years-230523500438</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C37" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D37" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Xmachines</v>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-xmachines-hyderabad-2-to-4-years-220824501724</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C38" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D38" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Pronix It Solutions</v>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-pronix-inc-hyderabad-1-to-4-years-170525501222</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C39" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D39" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Royal It Park Services</v>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-royal-it-park-services-hyderabad-2-to-5-years-151025503957</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C40" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D40" t="str">
+        <v>Full-Stack Developer</v>
+      </c>
+      <c r="E40" t="str">
+        <v>THE Patterns Company</v>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-the-patterns-company-hyderabad-2-to-6-years-150424501222</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C41" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D41" t="str">
+        <v>Full-Stack Developer</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Boxfinity</v>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-boxfinity-pvt-ltd-hyderabad-1-to-3-years-130423500280</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C42" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D42" t="str">
+        <v>Full Stack Developer React + Node</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Quanteon Solutions</v>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-react-node-quanteon-llc-hyderabad-3-to-8-years-130226502853</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C43" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D43" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Xmachines</v>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-xmachines-hyderabad-2-to-7-years-090824501158</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C44" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D44" t="str">
+        <v>Full - Stack Developer</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Techefficio</v>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-techefficio-hyderabad-3-to-5-years-220223503332</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C45" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Full Stack Developer - Ananta Labs</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Ananta Labs Rajkot</v>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-ananta-labs-ananta-labs-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-7-years-120725502501</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C46" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Adtcore</v>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-adtcore-hyderabad-2-to-7-years-181224501444</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C47" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E47" t="str">
+        <v>Datam Intelligence</v>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-datam-intelligence-hyderabad-3-to-8-years-061025500235</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C48" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Triad Square Infosec</v>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-triad-square-infotec-pvt-ltd-hyderabad-chennai-bengaluru-5-to-10-years-270625500180</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C49" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Capital Info</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-capital-now-hyderabad-4-to-9-years-091025503575</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C50" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Full Stack Developer (ReactJS/NodeJS)</v>
+      </c>
+      <c r="E50" t="str">
+        <v>Next Leap Innovtions</v>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-reactjs-nodejs-next-leap-innovtions-pvt-ltd-hyderabad-6-to-12-years-271123500261</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C51" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E51" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-210426916995</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C52" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Sr.Fullstack Developer (Consumer Experience) | Offshore |</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Photon</v>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>https://www.naukri.com/job-listings-sr-fullstack-developer-consumer-experience-offshore-photon-infotech-p-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-6-to-11-years-200525500791</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C53" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Full Stack Software Developer (React, Java/Node JS)</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Accellor Inc</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-software-developer-react-java-node-js-accellor-inc-hyderabad-3-to-5-years-070426501846</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C54" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E54" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928282</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C55" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928260</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C56" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928235</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C57" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928060</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C58" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928057</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C59" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928056</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C60" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Digirecruitx</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-digirecruitx-hyderabad-5-to-10-years-180226501408</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C61" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Prudent Globaltech Solutions</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-prudent-globaltech-solutions-private-limited-hyderabad-5-to-10-years-180226501088</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C62" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D62" t="str">
+        <v>AWS Full Stack Developer</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Programming.Com</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>https://www.naukri.com/job-listings-aws-full-stack-developer-programming-com-hyderabad-pune-coimbatore-bengaluru-5-to-9-years-121224501267</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C63" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D63" t="str">
+        <v>AI Full Stack Developer</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Pronix It Solutions</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>https://www.naukri.com/job-listings-ai-full-stack-developer-pronix-inc-hyderabad-4-to-6-years-040225505227</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C64" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Full stack Developers</v>
+      </c>
+      <c r="E64" t="str">
+        <v>O2labs Solutions</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developers-o2labs-solutions-hyderabad-4-to-8-years-030924501530</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C65" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426928288</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C66" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426928051</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C67" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426927808</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C68" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426927806</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C69" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426927576</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C70" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D70" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Proclink</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-proclink-consulting-services-llp-hyderabad-4-to-8-years-181225503637</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C71" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Full Stack Developer (ReactJS + NodeJS)</v>
+      </c>
+      <c r="E71" t="str">
+        <v>Religent Systems</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-reactjs-nodejs-religent-systems-hyderabad-4-to-6-years-081225503639</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C72" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Full Stack Developer Node js + Angular React + Python</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Cognine Technologies</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-node-js-angular-react-python-cognine-technologies-pvt-ltd-hyderabad-2-to-5-years-260226503607</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C73" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E73" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-020426930733</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C74" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-300326931255</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C75" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-15-to-20-years-210426919021</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C76" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-15-to-20-years-260326920889</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C77" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D77" t="str">
+        <v>Custom Software Engineer</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>https://www.naukri.com/job-listings-custom-software-engineer-accenture-solutions-pvt-ltd-hyderabad-5-to-10-years-020426928601</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C78" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Software Engineer (Mid-Level)</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Datamaze Solutions</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineer-mid-level-datamaze-solutions-hyderabad-3-to-5-years-231225502572</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C79" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D79" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Capco</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-capco-technologies-pvt-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-8-to-13-years-260326500669</v>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C80" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D80" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Tech Stalwart Solution</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-tech-stalwart-solution-private-limited-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-3-years-040225508253</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C81" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Ivanti</v>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineer-ivanti-hyderabad-3-to-7-years-130326502908</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C82" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Node JS Developer</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Ideyalabs Tech</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>https://www.naukri.com/job-listings-node-js-developer-ideyalabs-hyderabad-3-to-5-years-240426501868</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C83" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Full stack Developer / Architect</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Hire Bridge Consultancy</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-architect-hire-bridge-consultancy-hyderabad-10-to-20-years-190226505169</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C84" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Full Stack Developer (JavaScript, React, Node.js)</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Taksha X Onlin</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-javascript-react-node-js-taksha-x-onlin-private-limited-hyderabad-2-to-3-years-290725501895</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C85" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Full Stack .NET Developer</v>
+      </c>
+      <c r="E85" t="str">
+        <v>SIS Software</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-net-developer-sis-software-india-private-limited-hyderabad-3-to-6-years-230426504739</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C86" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-210426919509</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C87" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-210426916030</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C88" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D88" t="str">
+        <v>SDE - Accessibility Tools &amp; AI</v>
+      </c>
+      <c r="E88" t="str">
+        <v>Deque Systems</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>https://www.naukri.com/job-listings-sde-accessibility-tools-ai-deque-systems-hyderabad-2-to-4-years-210426501830</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C89" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Full Stack Developer- MERN</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Voiceoc Innovations</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-mern-voiceoc-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-4-years-201124513579</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C90" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Full Stack Developer (PHP, Laravel)</v>
+      </c>
+      <c r="E90" t="str">
+        <v>Cupid Knot</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-php-laravel-cupid-knot-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-0-to-3-years-130225506970</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C91" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E91" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-130426921041</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C92" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Senior E Commerce Developer</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Kontoor Brands, Inc.</v>
+      </c>
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <v>https://www.naukri.com/job-listings-senior-e-commerce-developer-kontoor-brands-inc-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-1-to-5-years-080925502962</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C93" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Sumpositive Services</v>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-sumpositive-llc-hyderabad-1-to-2-years-261125500966</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C94" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="E94" t="str">
+        <v>Creoquad Hyderabad</v>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-creoquad-hyderabad-3-to-6-years-220925505099</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C95" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="E95" t="str">
+        <v>Navishaa</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-navishaa-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-7-years-210725502168</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C96" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E96" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426927846</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C97" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-070426927814</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C98" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Developer (NodeJs/React-NextJs)</v>
+      </c>
+      <c r="E98" t="str">
+        <v>Photon</v>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <v>https://www.naukri.com/job-listings-developer-nodejs-react-nextjs-photon-infotech-p-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-10-years-170725502168</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C99" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Senior NodeJS Engineer (Work From Home)</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Finoit Technologies</v>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <v>https://www.naukri.com/job-listings-senior-nodejs-engineer-work-from-home-finoit-technologies-i-pvt-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-8-years-300924501714</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C100" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D100" t="str">
+        <v>AI Fullstack Engineer (Ruby and Python)</v>
+      </c>
+      <c r="E100" t="str">
+        <v>Infraveo Technologies</v>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <v>https://www.naukri.com/job-listings-ai-fullstack-engineer-ruby-and-python-infraveo-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-6-years-120725502404</v>
+      </c>
+      <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C101" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D101" t="str">
+        <v>Senior Full Stack Developer For Sora Union</v>
+      </c>
+      <c r="E101" t="str">
+        <v>Sora Union</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <v>https://www.naukri.com/job-listings-senior-full-stack-developer-for-sora-union-sora-union-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-6-years-100225503122</v>
+      </c>
+      <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C102" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D102" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E102" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326932464</v>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C103" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D103" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E103" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326932359</v>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C104" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D104" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E104" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-300326931740</v>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C105" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D105" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E105" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326930735</v>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C106" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D106" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E106" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326930613</v>
+      </c>
+      <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C107" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D107" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E107" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326926013</v>
+      </c>
+      <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C108" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D108" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E108" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-100426925530</v>
+      </c>
+      <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C109" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D109" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E109" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426928324</v>
+      </c>
+      <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C110" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D110" t="str">
+        <v>Software Development Engineer</v>
+      </c>
+      <c r="E110" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>https://www.naukri.com/job-listings-software-development-engineer-accenture-solutions-pvt-ltd-hyderabad-1-to-4-years-070426927797</v>
+      </c>
+      <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C111" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D111" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E111" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-070426927780</v>
+      </c>
+      <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C112" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D112" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E112" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-070426927228</v>
+      </c>
+      <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C113" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D113" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E113" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-060426923853</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C114" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D114" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E114" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-020426930403</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C115" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D115" t="str">
+        <v>MERN Stack Developer</v>
+      </c>
+      <c r="E115" t="str">
+        <v>Cogitate Technology Solutions</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
+        <v>https://www.naukri.com/job-listings-mern-stack-developer-cogitate-technology-solutions-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-7-years-220125501157</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C116" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D116" t="str">
+        <v>Jr Full Stack SW Engineer</v>
+      </c>
+      <c r="E116" t="str">
+        <v>Neev Systems</v>
+      </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v>https://www.naukri.com/job-listings-jr-full-stack-sw-engineer-neev-systems-hyderabad-3-to-5-years-150426501064</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C117" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D117" t="str">
+        <v>Senior Software Engineer ( React )</v>
+      </c>
+      <c r="E117" t="str">
+        <v>Hatica</v>
+      </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-react-hatica-mumbai-hyderabad-pune-gurugram-chennai-bengaluru-1-to-8-years-110423501832</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C118" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D118" t="str">
+        <v>Senior Software Engineer ( Node. js )</v>
+      </c>
+      <c r="E118" t="str">
+        <v>Hatica</v>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-node-js-hatica-mumbai-hyderabad-pune-gurugram-chennai-bengaluru-3-to-6-years-110423501831</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C119" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D119" t="str">
+        <v>Software Engineer (Full-Stack)</v>
+      </c>
+      <c r="E119" t="str">
+        <v>Brave Technologies</v>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineer-full-stack-braves-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-2-to-5-years-110326504408</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C120" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D120" t="str">
+        <v>Full Stack PHP Developer</v>
+      </c>
+      <c r="E120" t="str">
+        <v>Sriven Corporate Solutions</v>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-php-developer-sriven-corporate-solutions-hyderabad-2-to-10-years-230226500637</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C121" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D121" t="str">
+        <v>Software Developer (Frontend/Backend/Full Stack)</v>
+      </c>
+      <c r="E121" t="str">
+        <v>Straina Technologies</v>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v>https://www.naukri.com/job-listings-software-developer-frontend-backend-full-stack-straina-technologies-hyderabad-0-to-5-years-110725500478</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C122" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D122" t="str">
+        <v>ROKU Developer</v>
+      </c>
+      <c r="E122" t="str">
+        <v>Logic Planet</v>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v>https://www.naukri.com/job-listings-roku-developer-logicplanet-it-services-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-6-years-200226504831</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C123" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D123" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E123" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-3-to-8-years-300326932364</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C124" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D124" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E124" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326930749</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C125" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D125" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E125" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-2-to-5-years-300326930732</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C126" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D126" t="str">
+        <v>Next JS Developer</v>
+      </c>
+      <c r="E126" t="str">
+        <v>Add Technologies</v>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v>https://www.naukri.com/job-listings-next-js-developer-add-technologies-hyderabad-1-to-3-years-100426501383</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C127" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D127" t="str">
+        <v>Platform Engineer (Cloud Specialist)</v>
+      </c>
+      <c r="E127" t="str">
+        <v>Leokraft Technologies</v>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
+        <v>https://www.naukri.com/job-listings-platform-engineer-cloud-specialist-leokraft-technologies-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-6-years-210225503853</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C128" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D128" t="str">
+        <v>Full Stack Professional</v>
+      </c>
+      <c r="E128" t="str">
+        <v>Photon</v>
+      </c>
+      <c r="F128" t="str">
+        <v/>
+      </c>
+      <c r="G128" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-professional-photon-infotech-p-ltd-kolkata-mumbai-new-delhi-hyderabad-pune-chennai-bengaluru-3-to-7-years-040325501740</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C129" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D129" t="str">
+        <v>Full Stack Web Developer</v>
+      </c>
+      <c r="E129" t="str">
+        <v>Eumaxindia</v>
+      </c>
+      <c r="F129" t="str">
+        <v/>
+      </c>
+      <c r="G129" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-web-developer-eumaxindia-private-limited-madurai-kolkata-mumbai-new-delhi-hyderabad-tiruchirapalli-chennai-coimbatore-bengaluru-3-to-8-years-011123500994</v>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C130" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D130" t="str">
+        <v>Full Stack Developer Intern</v>
+      </c>
+      <c r="E130" t="str">
+        <v>Hawk Sense Business Solutions</v>
+      </c>
+      <c r="F130" t="str">
+        <v/>
+      </c>
+      <c r="G130" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-intern-hawk-sense-business-solutions-hyderabad-0-to-3-years-130126505593</v>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C131" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D131" t="str">
+        <v>Full stack Engineer - Java &amp; Angular/Vue</v>
+      </c>
+      <c r="E131" t="str">
+        <v>Apple</v>
+      </c>
+      <c r="F131" t="str">
+        <v/>
+      </c>
+      <c r="G131" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-java-angular-vue-apple-india-pvt-ltd-hyderabad-3-to-7-years-101125502084</v>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C132" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D132" t="str">
+        <v>Junior Software Developer (Node.js &amp; React)</v>
+      </c>
+      <c r="E132" t="str">
+        <v>The Dhan Academy</v>
+      </c>
+      <c r="F132" t="str">
+        <v/>
+      </c>
+      <c r="G132" t="str">
+        <v>https://www.naukri.com/job-listings-junior-software-developer-node-js-react-the-dhan-academy-hyderabad-1-to-4-years-061125500864</v>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C133" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D133" t="str">
+        <v>Junior Software Developer (Node.js &amp; React)</v>
+      </c>
+      <c r="E133" t="str">
+        <v>Dhan &amp; Co</v>
+      </c>
+      <c r="F133" t="str">
+        <v/>
+      </c>
+      <c r="G133" t="str">
+        <v>https://www.naukri.com/job-listings-junior-software-developer-node-js-react-dhan-co-hyderabad-0-to-5-years-140126502407</v>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C134" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D134" t="str">
+        <v>Lead UI Developer- React, Node.js</v>
+      </c>
+      <c r="E134" t="str">
+        <v>S&amp;P Global Inc.</v>
+      </c>
+      <c r="F134" t="str">
+        <v/>
+      </c>
+      <c r="G134" t="str">
+        <v>https://www.naukri.com/job-listings-lead-ui-developer-react-node-js-s-p-global-inc-noida-hyderabad-3-to-8-years-140225503119</v>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C135" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D135" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="E135" t="str">
+        <v>Kurakula's</v>
+      </c>
+      <c r="F135" t="str">
+        <v/>
+      </c>
+      <c r="G135" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-kurakulas-hyderabad-1-to-4-years-290725501819</v>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C136" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D136" t="str">
+        <v>Web Developer</v>
+      </c>
+      <c r="E136" t="str">
+        <v>Reinvision Labs</v>
+      </c>
+      <c r="F136" t="str">
+        <v/>
+      </c>
+      <c r="G136" t="str">
+        <v>https://www.naukri.com/job-listings-web-developer-reinvision-labs-pvt-ltd-hyderabad-3-to-4-years-041125504981</v>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C137" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D137" t="str">
+        <v>Full Stack Developer React and Ruby on Rails</v>
+      </c>
+      <c r="E137" t="str">
+        <v>Accellor Inc</v>
+      </c>
+      <c r="F137" t="str">
+        <v/>
+      </c>
+      <c r="G137" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-react-and-ruby-on-rails-accellor-inc-hyderabad-3-to-8-years-030326500258</v>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C138" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D138" t="str">
+        <v>Senior Software Engineer MEAN/MERN stack</v>
+      </c>
+      <c r="E138" t="str">
+        <v>Accordion Partners</v>
+      </c>
+      <c r="F138" t="str">
+        <v/>
+      </c>
+      <c r="G138" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-mean-mern-stack-accordion-partners-hyderabad-2-to-4-years-251025500341</v>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v>External — needs manual apply</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>27/4/2026, 2:03:06 pm</v>
+      </c>
+      <c r="C139" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D139" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E139" t="str">
+        <v>Priacc Innovations</v>
+      </c>
+      <c r="F139" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G139" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-priacc-innovations-hyderabad-2-to-6-years-130226503941</v>
+      </c>
+      <c r="H139" t="str">
+        <v>https://www.priaccinnovations.ai/careers.html</v>
+      </c>
+      <c r="I139" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>27/4/2026, 2:03:23 pm</v>
+      </c>
+      <c r="C140" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D140" t="str">
+        <v>Junior Nodejs Backend Developer</v>
+      </c>
+      <c r="E140" t="str">
+        <v>Remote Teams It Solutions</v>
+      </c>
+      <c r="F140" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G140" t="str">
+        <v>https://www.naukri.com/job-listings-junior-nodejs-backend-developer-remote-teams-it-solutions-hyderabad-1-to-6-years-240924502743</v>
+      </c>
+      <c r="H140" t="str">
+        <v>https://remote-teams.in/careers-2/</v>
+      </c>
+      <c r="I140" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>27/4/2026, 2:03:29 pm</v>
+      </c>
+      <c r="C141" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D141" t="str">
+        <v>MERN STACK DEVELOPER</v>
+      </c>
+      <c r="E141" t="str">
+        <v>Skygoal Tech</v>
+      </c>
+      <c r="F141" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G141" t="str">
+        <v>https://www.naukri.com/job-listings-mern-stack-developer-skygoaltech-hyderabad-3-to-5-years-180924503691</v>
+      </c>
+      <c r="H141" t="str">
+        <v>https://skygoaltech.zohorecruit.in/jobs/Careers/129788000000366001/Flutter-Developer?source=CareerSite</v>
+      </c>
+      <c r="I141" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>27/4/2026, 2:03:36 pm</v>
+      </c>
+      <c r="C142" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D142" t="str">
+        <v>AI/ML Solutions Engineer -</v>
+      </c>
+      <c r="E142" t="str">
+        <v>Pronix It Solutions</v>
+      </c>
+      <c r="F142" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G142" t="str">
+        <v>https://www.naukri.com/job-listings-ai-ml-solutions-engineer-pronix-inc-hyderabad-2-to-6-years-180225503531</v>
+      </c>
+      <c r="H142" t="str">
+        <v>https://jobsapi.ceipal.com/APISource/v1/index.html?bgcolor=1ba1ff&amp;api_key=RmN3WWEvUGF6ZTVpS0MxSTdhRnFqZz09&amp;cp_id=z5G7h3l6a1kMvyS65NP3cwRgTiAIalidLygk_Jn9L0A=</v>
+      </c>
+      <c r="I142" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>27/4/2026, 2:03:41 pm</v>
+      </c>
+      <c r="C143" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D143" t="str">
+        <v>Software Engineering Analyst - HIH - Evernorth</v>
+      </c>
+      <c r="E143" t="str">
+        <v>Cigna Medical Group</v>
+      </c>
+      <c r="F143" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G143" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineering-analyst-hih-evernorth-cigna-medical-group-hyderabad-1-to-3-years-090426502140</v>
+      </c>
+      <c r="H143" t="str">
+        <v>https://cigna.wd5.myworkdayjobs.com/en-US/cignacareers/job/Hyderabad-India/Software-Engineering-Analyst---HIH---Evernorth_26003300</v>
+      </c>
+      <c r="I143" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>27/4/2026, 2:03:47 pm</v>
+      </c>
+      <c r="C144" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D144" t="str">
+        <v>Python Full Stack Developer AI Platform Development</v>
+      </c>
+      <c r="E144" t="str">
+        <v>Mediamint</v>
+      </c>
+      <c r="F144" t="str">
+        <v>Hyderabad, Warangal, Nizamabad</v>
+      </c>
+      <c r="G144" t="str">
+        <v>https://www.naukri.com/job-listings-python-full-stack-developer-ai-platform-development-mediamint-warangal-hyderabad-nizamabad-3-to-5-years-011225505099</v>
+      </c>
+      <c r="H144" t="str">
+        <v>https://jobsapi.ceipal.com/APISource/v4/index.html?job_id=z5G7h3l6a1kMvyS65NP3cx9egwfyCFgWah7QB6_22fI=</v>
+      </c>
+      <c r="I144" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>27/4/2026, 2:03:53 pm</v>
+      </c>
+      <c r="C145" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D145" t="str">
+        <v>Jr. Fullstack Engineer (Node &amp; React)</v>
+      </c>
+      <c r="E145" t="str">
+        <v>Cloud Counselage</v>
+      </c>
+      <c r="F145" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G145" t="str">
+        <v>https://www.naukri.com/job-listings-jr-fullstack-engineer-node-react-cloud-counselage-pvt-ltd-hyderabad-2-to-8-years-301225508156</v>
+      </c>
+      <c r="H145" t="str">
+        <v>https://www.careers-page.com/cloud-counselage-pvt-ltd/job/QWV995XW</v>
+      </c>
+      <c r="I145" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>27/4/2026, 2:04:02 pm</v>
+      </c>
+      <c r="C146" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D146" t="str">
+        <v>React Developer</v>
+      </c>
+      <c r="E146" t="str">
+        <v>KTree</v>
+      </c>
+      <c r="F146" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G146" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-k-tree-computer-solutions-i-pvt-ltd-hyderabad-2-to-7-years-200126501935</v>
+      </c>
+      <c r="H146" t="str">
+        <v>https://ktree.com/jobs/react-developer</v>
+      </c>
+      <c r="I146" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>27/4/2026, 2:04:09 pm</v>
+      </c>
+      <c r="C147" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D147" t="str">
+        <v>Senior React Developer</v>
+      </c>
+      <c r="E147" t="str">
+        <v>KTree</v>
+      </c>
+      <c r="F147" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G147" t="str">
+        <v>https://www.naukri.com/job-listings-senior-react-developer-k-tree-computer-solutions-i-pvt-ltd-hyderabad-3-to-8-years-200126501417</v>
+      </c>
+      <c r="H147" t="str">
+        <v>https://ktree.com/jobs/senior-react-developer</v>
+      </c>
+      <c r="I147" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>27/4/2026, 2:04:17 pm</v>
+      </c>
+      <c r="C148" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D148" t="str">
+        <v>React Developer</v>
+      </c>
+      <c r="E148" t="str">
+        <v>KTree</v>
+      </c>
+      <c r="F148" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G148" t="str">
+        <v>https://www.naukri.com/job-listings-react-developer-k-tree-computer-solutions-i-pvt-ltd-hyderabad-3-to-8-years-200126501415</v>
+      </c>
+      <c r="H148" t="str">
+        <v>https://ktree.com/jobs/react-developer</v>
+      </c>
+      <c r="I148" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>27/4/2026, 2:04:29 pm</v>
+      </c>
+      <c r="C149" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D149" t="str">
+        <v>Developer, P&amp;C Technology</v>
+      </c>
+      <c r="E149" t="str">
+        <v>Warner Bros. Discovery</v>
+      </c>
+      <c r="F149" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G149" t="str">
+        <v>https://www.naukri.com/job-listings-developer-p-c-technology-warner-bros-discovery-hyderabad-3-to-8-years-200126508852</v>
+      </c>
+      <c r="H149" t="str">
+        <v>https://warnerbros.wd5.myworkdayjobs.com/en-US/global/job/Hyderabad-Office-Level-3--4-Block-A---East-Wing/Developer--P-C-Technology_R000099895</v>
+      </c>
+      <c r="I149" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>27/4/2026, 2:04:35 pm</v>
+      </c>
+      <c r="C150" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D150" t="str">
+        <v>Next.js Developer</v>
+      </c>
+      <c r="E150" t="str">
+        <v>Aptagrim Consulting</v>
+      </c>
+      <c r="F150" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G150" t="str">
+        <v>https://www.naukri.com/job-listings-next-js-developer-aptagrim-consulting-llp-hyderabad-2-to-5-years-270126502938</v>
+      </c>
+      <c r="H150" t="str">
+        <v>https://applicant-enterprise.psyhire.ai/jobs/APTO1J144?company_id=APTO1</v>
+      </c>
+      <c r="I150" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151" t="str">
+        <v>27/4/2026, 2:04:39 pm</v>
+      </c>
+      <c r="C151" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D151" t="str">
+        <v>Full Stack Engineer</v>
+      </c>
+      <c r="E151" t="str">
+        <v>Overture Rede</v>
+      </c>
+      <c r="F151" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G151" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-overture-rede-pvt-ltd-hyderabad-3-to-7-years-200326501635</v>
+      </c>
+      <c r="H151" t="str">
+        <v>https://overturerede.zohorecruit.in/jobs/Careers/58988000017219239</v>
+      </c>
+      <c r="I151" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152" t="str">
+        <v>27/4/2026, 2:04:45 pm</v>
+      </c>
+      <c r="C152" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D152" t="str">
+        <v>Sr Associate Software Engineer</v>
+      </c>
+      <c r="E152" t="str">
+        <v>Amgen Inc</v>
+      </c>
+      <c r="F152" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G152" t="str">
+        <v>https://www.naukri.com/job-listings-sr-associate-software-engineer-horizon-therapeutics-hyderabad-1-to-9-years-210525500810</v>
+      </c>
+      <c r="H152" t="str">
+        <v>https://amgen.wd1.myworkdayjobs.com/en-US/Careers/job/India---Hyderabad/Sr-Associate-Software-Engineer_R-194482</v>
+      </c>
+      <c r="I152" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153" t="str">
+        <v>27/4/2026, 2:04:49 pm</v>
+      </c>
+      <c r="C153" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D153" t="str">
+        <v>Java full stack developer</v>
+      </c>
+      <c r="E153" t="str">
+        <v>CBL Solutions</v>
+      </c>
+      <c r="F153" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G153" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-dataskate-hyderabad-3-to-5-years-271023500143</v>
+      </c>
+      <c r="H153" t="str">
+        <v>https://app.pyjamahr.com/careers?company=cblsolutions&amp;job_id=54001&amp;company_uuid=6671212097</v>
+      </c>
+      <c r="I153" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154" t="str">
+        <v>27/4/2026, 2:04:54 pm</v>
+      </c>
+      <c r="C154" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D154" t="str">
+        <v>UI Developer</v>
+      </c>
+      <c r="E154" t="str">
+        <v>Amgen Inc</v>
+      </c>
+      <c r="F154" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G154" t="str">
+        <v>https://www.naukri.com/job-listings-ui-developer-horizon-therapeutics-hyderabad-1-to-9-years-210525500909</v>
+      </c>
+      <c r="H154" t="str">
+        <v>https://amgen.wd1.myworkdayjobs.com/en-US/Careers/job/India---Hyderabad/UI-Developer_R-208531</v>
+      </c>
+      <c r="I154" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155" t="str">
+        <v>27/4/2026, 2:05:02 pm</v>
+      </c>
+      <c r="C155" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D155" t="str">
+        <v>Senior Front End Developer</v>
+      </c>
+      <c r="E155" t="str">
+        <v>Ice.com</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G155" t="str">
+        <v>https://www.naukri.com/job-listings-senior-front-end-developer-ice-com-hyderabad-2-to-6-years-171025501063</v>
+      </c>
+      <c r="H155" t="str">
+        <v>https://careers.ice.com/jobs/11311?lang=en-us</v>
+      </c>
+      <c r="I155" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156" t="str">
+        <v>27/4/2026, 2:05:08 pm</v>
+      </c>
+      <c r="C156" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D156" t="str">
+        <v>Vue Js Developer</v>
+      </c>
+      <c r="E156" t="str">
+        <v>Nava Software Solutions</v>
+      </c>
+      <c r="F156" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G156" t="str">
+        <v>https://www.naukri.com/job-listings-vue-js-developer-nava-software-solutions-hyderabad-2-to-5-years-110423500526</v>
+      </c>
+      <c r="H156" t="str">
+        <v>https://jobsapi.ceipal.com/APISource/v2/index.html?job_id=z5G7h3l6a1kMvyS65NP3c-dtHM5o24pASCsNqJGnSMw=</v>
+      </c>
+      <c r="I156" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157" t="str">
+        <v>27/4/2026, 2:05:12 pm</v>
+      </c>
+      <c r="C157" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D157" t="str">
+        <v>Java full stack developer</v>
+      </c>
+      <c r="E157" t="str">
+        <v>CBL Solutions</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G157" t="str">
+        <v>https://www.naukri.com/job-listings-java-full-stack-developer-cbl-solutions-hyderabad-3-to-5-years-090923500127</v>
+      </c>
+      <c r="H157" t="str">
+        <v>https://app.pyjamahr.com/careers?company=company&amp;job_id=54001&amp;company_uuid=6671212097</v>
+      </c>
+      <c r="I157" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158" t="str">
+        <v>27/4/2026, 2:05:17 pm</v>
+      </c>
+      <c r="C158" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D158" t="str">
+        <v>Electron JS Developer</v>
+      </c>
+      <c r="E158" t="str">
+        <v>BTF Technology</v>
+      </c>
+      <c r="F158" t="str">
+        <v>Hyderabad, Mysuru</v>
+      </c>
+      <c r="G158" t="str">
+        <v>https://www.naukri.com/job-listings-electron-js-developer-btf-technology-hyderabad-mysuru-3-to-5-years-031024500482</v>
+      </c>
+      <c r="H158" t="str">
+        <v>https://btfpeople.com/careers/electron-js-developer/</v>
+      </c>
+      <c r="I158" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159" t="str">
+        <v>27/4/2026, 2:05:23 pm</v>
+      </c>
+      <c r="C159" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D159" t="str">
+        <v>Application Developer</v>
+      </c>
+      <c r="E159" t="str">
+        <v>Accenture</v>
+      </c>
+      <c r="F159" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G159" t="str">
+        <v>https://www.naukri.com/job-listings-application-developer-accenture-solutions-pvt-ltd-hyderabad-15-to-20-years-220426926980</v>
+      </c>
+      <c r="H159" t="str">
+        <v>https://www.accenture.com/in-en/careers/jobdetails?id=ATCI-4924037-S1869773_en&amp;title=Application+Developer&amp;SRC=RECNau</v>
+      </c>
+      <c r="I159" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160" t="str">
+        <v>27/4/2026, 2:05:39 pm</v>
+      </c>
+      <c r="C160" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D160" t="str">
+        <v>Senior Full Stack Engineer (React / Node.js)</v>
+      </c>
+      <c r="E160" t="str">
+        <v>Amgen Inc</v>
+      </c>
+      <c r="F160" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G160" t="str">
+        <v>https://www.naukri.com/job-listings-senior-full-stack-engineer-react-node-js-amgen-inc-hyderabad-8-to-12-years-210426927575</v>
+      </c>
+      <c r="H160" t="str">
+        <v>https://careers.amgen.com/en/job/-/-/87/89015058000?source=rd_naukri&amp;utm_source=naukri.com&amp;utm_medium=job_posting&amp;utm_campaign=Healthcare_General&amp;utm_content=job_board&amp;utm_term=402434614&amp;ss=paid</v>
+      </c>
+      <c r="I160" t="str">
+        <v>External — apply manually</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161" t="str">
+        <v>27/4/2026, 2:06:26 pm</v>
+      </c>
+      <c r="C161" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D161" t="str">
+        <v>Associate Software Engineer</v>
+      </c>
+      <c r="E161" t="str">
+        <v>Knowledgesprint Technologies</v>
+      </c>
+      <c r="F161" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G161" t="str">
+        <v>https://www.naukri.com/job-listings-associate-software-engineer-knowledgesprint-technologies-india-pvt-ltd-hyderabad-0-to-4-years-030426506143</v>
+      </c>
+      <c r="H161" t="str">
+        <v>https://knowledgesprint.com/careers</v>
+      </c>
+      <c r="I161" t="str">
+        <v>External — apply manually</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I161"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="4.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
-    <col min="7" max="7" width="50.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -941,18 +6700,75 @@
         <v>Date</v>
       </c>
       <c r="C1" t="str">
+        <v>Source</v>
+      </c>
+      <c r="D1" t="str">
         <v>Job Title</v>
       </c>
+      <c r="E1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Apply URL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>External URL</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Notes / Reason</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I99"/>
+  <cols>
+    <col min="1" max="1" width="4.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="60.83203125" customWidth="1"/>
+    <col min="8" max="8" width="60.83203125" customWidth="1"/>
+    <col min="9" max="9" width="50.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>#</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Date</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Source</v>
+      </c>
       <c r="D1" t="str">
+        <v>Job Title</v>
+      </c>
+      <c r="E1" t="str">
         <v>Company</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Location</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Apply URL</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>External URL</v>
+      </c>
+      <c r="I1" t="str">
         <v>Notes / Reason</v>
       </c>
     </row>
@@ -961,22 +6777,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>25/4/2026, 5:26:27 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C2" t="str">
-        <v>Front End Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D2" t="str">
-        <v>INRY / Cprime</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>Hyderabad, India</v>
+        <v/>
       </c>
       <c r="F2" t="str">
-        <v>https://jobs.lever.co/cprime/e5fd1d68-34c3-4120-b247-e6ac94c2c339/apply</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>Drupal-specific — not in resume</v>
+        <v>https://www.skillzenloop.com/jobs</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="3">
@@ -984,22 +6806,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>25/4/2026, 5:26:46 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C3" t="str">
-        <v>MERN Stack Intern</v>
+        <v>linkedin</v>
       </c>
       <c r="D3" t="str">
-        <v>ArGo Intern</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>India</v>
+        <v/>
       </c>
       <c r="F3" t="str">
-        <v>https://docs.google.com/forms/d/1hlDHW7LAztvcS27-FWcOW5pPRRYcxZeu8K30p</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>Form 404 - expired</v>
+        <v>https://docs.google.com/forms/d/1hlDHW7LAztvcS27-FWcOW5pPRRYcxZeu8K30pOwGn0w</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="4">
@@ -1007,22 +6835,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>25/4/2026, 5:28:22 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C4" t="str">
-        <v>Front-End Developer Intern</v>
+        <v>linkedin</v>
       </c>
       <c r="D4" t="str">
-        <v>Dexter's Tech</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>India</v>
+        <v/>
       </c>
       <c r="F4" t="str">
-        <v>https://form.webboostsolutions.in/</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>Internship — not applicable</v>
+        <v>https://inficoresofts.com/jobs</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="5">
@@ -1030,22 +6864,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>25/4/2026, 5:28:22 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C5" t="str">
-        <v>MERN Stack Intern</v>
+        <v>linkedin</v>
       </c>
       <c r="D5" t="str">
-        <v>ArGo Intern</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>India</v>
+        <v/>
       </c>
       <c r="F5" t="str">
-        <v>https://docs.google.com/forms/...</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>Internship — not applicable</v>
+        <v>https://www.hirecrap.com/job-description-ina/15820_4403467877?src=LinkedIn</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="6">
@@ -1053,22 +6893,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>25/4/2026, 5:28:22 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C6" t="str">
-        <v>Front End Developer Intern</v>
+        <v>linkedin</v>
       </c>
       <c r="D6" t="str">
-        <v>Skillzenloop</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>India</v>
+        <v/>
       </c>
       <c r="F6" t="str">
-        <v>https://www.skillzenloop.com/jobs</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>Internship — not applicable</v>
+        <v>https://pinakeedigitaltechnology.com/jobs/web-developer/</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="7">
@@ -1076,22 +6922,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>25/4/2026, 5:28:22 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C7" t="str">
-        <v>MERN Stack Developer Intern</v>
+        <v>linkedin</v>
       </c>
       <c r="D7" t="str">
-        <v>Inficore Soft</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>India</v>
+        <v/>
       </c>
       <c r="F7" t="str">
-        <v>https://inficoresofts.com/jobs</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>Internship — not applicable</v>
+        <v>https://goodyear.wd1.myworkdayjobs.com/GoodyearCareers/job/IN-Hyderabad/Web-Developer_JR-40106702?source=LinkedIn</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="8">
@@ -1099,22 +6951,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>25/4/2026, 6:47:04 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C8" t="str">
-        <v>Frontend Web Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D8" t="str">
-        <v>MeridianSquare (via FetchJobs/hirecrap)</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>North Goa, Goa, India</v>
+        <v/>
       </c>
       <c r="F8" t="str">
-        <v>https://www.hirecrap.com/job-description-ina/15820_4403467877</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>Location Goa — not in preferred cities (Hyderabad/Bangalore) and not remote</v>
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33193&amp;s=ads_developers_linkedinJobs</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="9">
@@ -1122,22 +6980,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>25/4/2026, 6:47:25 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C9" t="str">
-        <v>Java Developer (listed as Web Developer)</v>
+        <v>linkedin</v>
       </c>
       <c r="D9" t="str">
-        <v>Pinakee Digital Technology</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>Bhubaneswar, Odisha</v>
+        <v/>
       </c>
       <c r="F9" t="str">
-        <v>https://pinakeedigitaltechnology.com/jobs/web-developer/</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>Java Developer role — 0 years Java experience; not a match</v>
+        <v>https://jobs.keyrus.co.uk/jobs/7634937-full-stack-developer-react-java</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="10">
@@ -1145,22 +7009,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>25/4/2026, 6:49:20 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C10" t="str">
-        <v>Web Developer</v>
+        <v>linkedin</v>
       </c>
       <c r="D10" t="str">
-        <v>Goodyear</v>
+        <v/>
       </c>
       <c r="E10" t="str">
-        <v>Hyderabad, India</v>
+        <v/>
       </c>
       <c r="F10" t="str">
-        <v>https://goodyear.wd1.myworkdayjobs.com/GoodyearCareers/job/IN-Hyderabad/Web-Developer_JR-40106702</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>Requires 6-9 years experience; Manoj has 2 years</v>
+        <v>https://jobs.smartrecruiters.com/QADInc/744000106075575-senior-software-engineer-full-stack?gns=LinkedInSlots</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>Skipped - internship/wrong role/location</v>
       </c>
     </row>
     <row r="11">
@@ -1168,22 +7038,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>25/4/2026, 6:53:57 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C11" t="str">
-        <v>Remote Full-Stack Developer (JS/TS)</v>
+        <v>linkedin</v>
       </c>
       <c r="D11" t="str">
-        <v>Turing</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>Remote, India (multiple cities)</v>
+        <v/>
       </c>
       <c r="F11" t="str">
-        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>Freelance contractor platform — requires account creation + 75-min technical interview; not a direct apply</v>
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33193&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33193</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>Turing freelance platform - not direct apply</v>
       </c>
     </row>
     <row r="12">
@@ -1191,22 +7067,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>25/4/2026, 7:05:25 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C12" t="str">
-        <v>Full Stack Developer (React + Java)</v>
+        <v>linkedin</v>
       </c>
       <c r="D12" t="str">
-        <v>Keyrus</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>Pune/Bangalore, India</v>
+        <v/>
       </c>
       <c r="F12" t="str">
-        <v>https://jobs.keyrus.co.uk/jobs/7634937-full-stack-developer-react-java</v>
+        <v/>
       </c>
       <c r="G12" t="str">
-        <v>Requires 5+ years + Java expertise; Manoj has 0 Java experience and 2 years total</v>
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33183&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33183</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>Turing freelance platform - not direct apply</v>
       </c>
     </row>
     <row r="13">
@@ -1214,27 +7096,2527 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>25/4/2026, 7:05:52 pm</v>
+        <v>25/4/2026, 3:30:00 pm</v>
       </c>
       <c r="C13" t="str">
-        <v>Senior Software Engineer - Full Stack</v>
+        <v>linkedin</v>
       </c>
       <c r="D13" t="str">
-        <v>QAD Inc</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>Pune, India</v>
+        <v/>
       </c>
       <c r="F13" t="str">
-        <v>https://jobs.smartrecruiters.com/QADInc/744000106075575-senior-software-engineer-full-stack</v>
+        <v/>
       </c>
       <c r="G13" t="str">
-        <v>Requires 8+ years experience; Manoj has 2 years</v>
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33184&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33184</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C14" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33195&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33195</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C15" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33185&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33185</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C16" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33188&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33188</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C17" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33190&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33190</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C18" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33190&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33190</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C19" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33189&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33189</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C20" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33193&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33193</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C21" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33194&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33194</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C22" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33186&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33186</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C23" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33191&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33191</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C24" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33195&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33195</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C25" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33192&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33192</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C26" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33186&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33186</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C27" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33193&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33193</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C28" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33182&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=mumbai&amp;job_id=33182</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="str">
+        <v>25/4/2026, 3:30:00 pm</v>
+      </c>
+      <c r="C29" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33191&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Kolkata&amp;job_id=33191</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v>Turing freelance platform - not direct apply</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>26/4/2026, 12:03:21 pm</v>
+      </c>
+      <c r="C30" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>https://form.webboostsolutions.in/</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="str">
+        <v>26/4/2026, 12:04:15 pm</v>
+      </c>
+      <c r="C31" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>https://careers.google.com/jobs/results/108040519686202054-senior-software-engineer/?src=Online/LinkedIn/linkedin_us&amp;utm_source=linkedin&amp;utm_medium=jobposting&amp;utm_campaign=contract</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="str">
+        <v>26/4/2026, 12:18:08 pm</v>
+      </c>
+      <c r="C32" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15161-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="str">
+        <v>26/4/2026, 12:44:08 pm</v>
+      </c>
+      <c r="C33" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>https://careers.ey.com/ey/job/Gurgaon-DE-React-Senior-Developer-GDSF02-HR-122010/1277970701/?feedId=337401&amp;utm_source=LinkedInJobPostings&amp;utm_campaign=j2w_linkedin</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="str">
+        <v>26/4/2026, 12:44:49 pm</v>
+      </c>
+      <c r="C34" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>https://cio.economictimes.indiatimes.com/jobs/business-development-manager/907853</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="str">
+        <v>26/4/2026, 12:52:03 pm</v>
+      </c>
+      <c r="C35" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>https://cutshort.io/job/Tech-Lead-Pune-Nirmitee-io-LpwQsnsz?utm_source=linkedin-feed&amp;utm_medium=xml&amp;utm_content=job-posting&amp;applicationsource=linkedin-feed</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="str">
+        <v>26/4/2026, 12:59:14 pm</v>
+      </c>
+      <c r="C36" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>https://www.jobs-ups.com/global/en/job/UPBUPSGLOBALR26003987EXTERNALENGLOBAL/Front-End-Developer-Angular?utm_source=linkedin&amp;utm_medium=phenom-feeds</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="str">
+        <v>26/4/2026, 12:59:56 pm</v>
+      </c>
+      <c r="C37" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>https://www.jobs-ups.com/imea/en/job/UPBUPSGLOBALR26003987EXTERNALENIMEA/Front-End-Developer-Angular?utm_source=linkedin&amp;utm_medium=phenom-feeds</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="str">
+        <v>26/4/2026, 1:00:08 pm</v>
+      </c>
+      <c r="C38" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15172-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="str">
+        <v>26/4/2026, 1:06:52 pm</v>
+      </c>
+      <c r="C39" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15165-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="str">
+        <v>26/4/2026, 1:15:16 pm</v>
+      </c>
+      <c r="C40" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>https://docs.google.com/forms/d/1hlDHW7LAztvcS27-FWcOW5pPRRYcxZeu8K30pOwGn0w/edit#settings</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="str">
+        <v>26/4/2026, 1:21:20 pm</v>
+      </c>
+      <c r="C41" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>https://careers.slb.com/jobdescription.aspx?id=EF15166-en_US+1&amp;utm_source=linkedin&amp;utm_medium=linkedin_posting&amp;utm_campaign=linkedin_career_posting&amp;src=LinkedIn</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="str">
+        <v>26/4/2026, 7:28:22 pm</v>
+      </c>
+      <c r="C42" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>https://www.instahyre.com/job-418591-web-developer-at-pencil-bitz-coimbatore/?utm_source=linkedin&amp;utm_medium=organic&amp;utm_campaign=linkedin_apply&amp;utm_term=418591</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="str">
+        <v>26/4/2026, 7:53:11 pm</v>
+      </c>
+      <c r="C43" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33196&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33196</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="str">
+        <v>26/4/2026, 7:53:46 pm</v>
+      </c>
+      <c r="C44" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33194&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33194</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="str">
+        <v>26/4/2026, 7:53:48 pm</v>
+      </c>
+      <c r="C45" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D45" t="str">
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33189&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;country=India&amp;job_id=33189</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="str">
+        <v>26/4/2026, 8:02:15 pm</v>
+      </c>
+      <c r="C46" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D46" t="str">
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33186&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33186</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="str">
+        <v>26/4/2026, 8:05:39 pm</v>
+      </c>
+      <c r="C47" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D47" t="str">
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33191&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33191</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="str">
+        <v>26/4/2026, 8:05:47 pm</v>
+      </c>
+      <c r="C48" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D48" t="str">
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33185&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33185</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="str">
+        <v>26/4/2026, 8:05:48 pm</v>
+      </c>
+      <c r="C49" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D49" t="str">
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33187&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Bengaluru&amp;job_id=33187</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="str">
+        <v>26/4/2026, 8:05:49 pm</v>
+      </c>
+      <c r="C50" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D50" t="str">
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33190&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33190</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="str">
+        <v>26/4/2026, 8:05:53 pm</v>
+      </c>
+      <c r="C51" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D51" t="str">
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <v>https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33195&amp;s=ads_developers_linkedinJobs&amp;n=https://developers.turing.com/direct-apply/JSOClCQN5arG?&amp;city=Hyderabad&amp;job_id=33195</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="str">
+        <v>26/4/2026, 8:06:21 pm</v>
+      </c>
+      <c r="C52" t="str">
+        <v>linkedin</v>
+      </c>
+      <c r="D52" t="str">
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <v>https://careers.ses.com/job/Chennai-Senior-Developer%2C-The-Link/1163033001/</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C53" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Walk-in || Fullstack Developer</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Spack Solutions</v>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-spack-solutions-hyderabad-2-to-4-years-250426013238</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v>no_apply_button</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C54" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Developer Jobs In Hyderabad Secunderabad</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-blueapplecloud-technologies-hyderabad-0-to-3-years-270426004459</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v>no_apply_button</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C55" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E55" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-cerebra-hyderabad-8-to-11-years-240426026278</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C56" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E56" t="str">
+        <v>GSPANN</v>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-gspann-hyderabad-pune-bengaluru-5-to-10-years-060426009455</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C57" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D57" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E57" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-cerebra-hyderabad-8-to-10-years-230426016453</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C58" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Fullstack Developer / (AI-Agentic Workflows)</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Infologitech</v>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-ai-agentic-workflows-infologitech-hyderabad-bengaluru-delhi-ncr-7-to-12-years-220426038807</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C59" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E59" t="str">
+        <v>Mastech Digital</v>
+      </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-mastech-digital-hyderabad-4-to-6-years-210426040031</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C60" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E60" t="str">
+        <v>Prudent Globaltech Solutions</v>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-prudent-globaltech-solutions-hyderabad-7-to-12-years-050326026896</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C61" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D61" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E61" t="str">
+        <v>Digitide Solutions</v>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-digitide-noida-mumbai-hyderabad-5-to-10-years-210426039466</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C62" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D62" t="str">
+        <v>Fullstack Developer-Noida and Hyderabad-25th April -F2F</v>
+      </c>
+      <c r="E62" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-noida-and-hyderabad-25th-april-f2f-cerebra-noida-hyderabad-8-to-13-years-210426041108</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C63" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D63" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E63" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-cerebra-hyderabad-chennai-bengaluru-6-to-8-years-200426019317</v>
+      </c>
+      <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C64" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D64" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E64" t="str">
+        <v>Radiant Digital Solutions</v>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-radiant-digital-solutions-hyderabad-4-to-8-years-170426024958</v>
+      </c>
+      <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C65" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D65" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E65" t="str">
+        <v>Tata Consultancy Services</v>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-tata-consultancy-services-hyderabad-chennai-bengaluru-5-to-10-years-170426015977</v>
+      </c>
+      <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C66" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D66" t="str">
+        <v>Python Developer</v>
+      </c>
+      <c r="E66" t="str">
+        <v>Loginsoft</v>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <v>https://www.naukri.com/job-listings-python-developer-loginsoft-hyderabad-2-to-5-years-010426022554</v>
+      </c>
+      <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C67" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D67" t="str">
+        <v>Senior Java Full Stack Developer with Agentic AI</v>
+      </c>
+      <c r="E67" t="str">
+        <v>Infologitech</v>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <v>https://www.naukri.com/job-listings-senior-java-full-stack-developer-with-agentic-ai-infologitech-hyderabad-8-to-12-years-130426010286</v>
+      </c>
+      <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C68" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D68" t="str">
+        <v>Devops Engineer</v>
+      </c>
+      <c r="E68" t="str">
+        <v>Qentelli</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v>https://www.naukri.com/job-listings-devops-engineer-qentelli-hyderabad-7-to-8-years-240426028278</v>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C69" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D69" t="str">
+        <v>Full Stack Developer</v>
+      </c>
+      <c r="E69" t="str">
+        <v>Siro Clinpharm</v>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-siro-clinpharm-hyderabad-delhi-ncr-mumbai-all-areas-4-to-6-years-060426002176</v>
+      </c>
+      <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C70" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D70" t="str">
+        <v>AWS Full Stack Developer</v>
+      </c>
+      <c r="E70" t="str">
+        <v>Mobile Programming</v>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <v>https://www.naukri.com/job-listings-aws-full-stack-developer-mobileprogramming-hyderabad-pune-coimbatore-bengaluru-5-to-9-years-020824500589</v>
+      </c>
+      <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C71" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D71" t="str">
+        <v>Fullstack Developer</v>
+      </c>
+      <c r="E71" t="str">
+        <v>GSPANN</v>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-gspann-hyderabad-pune-delhi-ncr-5-to-10-years-070426017679</v>
+      </c>
+      <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C72" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D72" t="str">
+        <v>Java Developer</v>
+      </c>
+      <c r="E72" t="str">
+        <v>Emagia</v>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>https://www.naukri.com/job-listings-java-developer-emagia-hyderabad-6-to-8-years-220426013268</v>
+      </c>
+      <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C73" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D73" t="str">
+        <v>Gen AI Architect</v>
+      </c>
+      <c r="E73" t="str">
+        <v>MBR Informatics</v>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <v>https://www.naukri.com/job-listings-gen-ai-architect-mbr-informatics-hyderabad-3-to-5-years-130426027884</v>
+      </c>
+      <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C74" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D74" t="str">
+        <v>Fullstack Developer (React+ Node)</v>
+      </c>
+      <c r="E74" t="str">
+        <v>Zetamicron Technologies</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-developer-react-node-zetamicron-technologies-hyderabad-bengaluru-8-to-10-years-100426013742</v>
+      </c>
+      <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C75" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D75" t="str">
+        <v>Node JS &amp; React -Full Stack Developer</v>
+      </c>
+      <c r="E75" t="str">
+        <v>Bounteous x Accolite</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <v>https://www.naukri.com/job-listings-node-js-react-full-stack-developer-bounteous-x-accolite-hyderabad-gurugram-bengaluru-5-to-10-years-180426015860</v>
+      </c>
+      <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C76" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D76" t="str">
+        <v>Full Stack Developer -Angular | Node.js | React.js - Immediate /Notice</v>
+      </c>
+      <c r="E76" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-angular-node-js-react-js-immediate-notice-cerebra-hyderabad-chennai-bengaluru-6-to-8-years-160426034518</v>
+      </c>
+      <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C77" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D77" t="str">
+        <v>.NET Architect</v>
+      </c>
+      <c r="E77" t="str">
+        <v>Callaway Digital Technologies</v>
+      </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v>https://www.naukri.com/job-listings-net-architect-callaway-digital-technologies-hyderabad-12-to-15-years-090426016040</v>
+      </c>
+      <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C78" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D78" t="str">
+        <v>Devops Architect</v>
+      </c>
+      <c r="E78" t="str">
+        <v>Processq India</v>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <v>https://www.naukri.com/job-listings-devops-architect-processq-india-hyderabad-12-to-20-years-070426019022</v>
+      </c>
+      <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C79" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D79" t="str">
+        <v>MERN Stack Developer</v>
+      </c>
+      <c r="E79" t="str">
+        <v>Adengage</v>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <v>https://www.naukri.com/job-listings-mern-stack-developer-adengage-mumbai-hyderabad-mumbai-hyderabad-3-to-5-years-240426923186</v>
+      </c>
+      <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C80" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D80" t="str">
+        <v>MERN Stack Developer (Intern)</v>
+      </c>
+      <c r="E80" t="str">
+        <v>Adengage</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <v>https://www.naukri.com/job-listings-mern-stack-developer-intern-adengage-mumbai-hyderabad-mumbai-hyderabad-0-to-1-years-210426909779</v>
+      </c>
+      <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C81" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D81" t="str">
+        <v>Optimizely Spire Developer</v>
+      </c>
+      <c r="E81" t="str">
+        <v>Leading Client</v>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <v>https://www.naukri.com/job-listings-optimizely-spire-developer-ideslabs-private-limited-hyderabad-5-to-10-years-220426929783</v>
+      </c>
+      <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C82" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D82" t="str">
+        <v>Software Engineer</v>
+      </c>
+      <c r="E82" t="str">
+        <v>Xpheno</v>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <v>https://www.naukri.com/job-listings-software-engineer-xpheno-hyderabad-5-to-10-years-160426034178</v>
+      </c>
+      <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C83" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D83" t="str">
+        <v>Full Stack Intern</v>
+      </c>
+      <c r="E83" t="str">
+        <v>Tensorgo Technologies</v>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-intern-tensorgo-technologies-hyderabad-0-to-1-years-310326912193</v>
+      </c>
+      <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C84" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D84" t="str">
+        <v>Associate Software Engineering(.Net)</v>
+      </c>
+      <c r="E84" t="str">
+        <v>Embarkgcc Services</v>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <v>https://www.naukri.com/job-listings-associate-software-engineering-net-embarkgcc-services-private-limited-hyderabad-3-to-5-years-070426026476</v>
+      </c>
+      <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C85" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D85" t="str">
+        <v>Content Lead - Full Stack Development</v>
+      </c>
+      <c r="E85" t="str">
+        <v>Bytexl Teched</v>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v>https://www.naukri.com/job-listings-content-lead-full-stack-development-bytexl-teched-hyderabad-3-to-5-years-100426018381</v>
+      </c>
+      <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C86" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D86" t="str">
+        <v>Junior Developer (ReactJS / TypeScript / Node.js)</v>
+      </c>
+      <c r="E86" t="str">
+        <v>Template.net</v>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v>https://www.naukri.com/job-listings-junior-developer-reactjs-typescript-node-js-template-net-hyderabad-1-to-3-years-010426016133</v>
+      </c>
+      <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C87" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D87" t="str">
+        <v>Consultant - Software Engineer (only For Hyderabad)</v>
+      </c>
+      <c r="E87" t="str">
+        <v>Embarkgcc Services</v>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>https://www.naukri.com/job-listings-consultant-software-engineer-only-for-hyderabad-embarkgcc-services-hyderabad-8-to-10-years-220426014431</v>
+      </c>
+      <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
+        <v>chatbot_unknown</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C88" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D88" t="str">
+        <v>Senior Software Developer (AI Energy)</v>
+      </c>
+      <c r="E88" t="str">
+        <v>S&amp;P Global Market Intelligence</v>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-developer-ai-energy-s-p-capital-iq-india-pvt-ltd-noida-hyderabad-3-to-8-years-070426920443</v>
+      </c>
+      <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C89" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D89" t="str">
+        <v>Permanent Role For Python with React @Hyderabad</v>
+      </c>
+      <c r="E89" t="str">
+        <v>Deloitte Consulting</v>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v>https://www.naukri.com/job-listings-permanent-role-for-python-with-react-hyderabad-deloitte-consulting-hyderabad-3-to-6-years-100426024819</v>
+      </c>
+      <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C90" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D90" t="str">
+        <v>Full Stack Engineer (Intern)</v>
+      </c>
+      <c r="E90" t="str">
+        <v>TensorGo</v>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-engineer-intern-tensorgo-hyderabad-0-to-2-years-270326928894</v>
+      </c>
+      <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>27/4/2026, 2:02:20 pm</v>
+      </c>
+      <c r="C91" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D91" t="str">
+        <v>Next.js / NestJS Developer</v>
+      </c>
+      <c r="E91" t="str">
+        <v>KTree</v>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v>https://www.naukri.com/job-listings-next-js-nestjs-developer-ktree-hyderabad-1-to-5-years-140426027447</v>
+      </c>
+      <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
+        <v>unknown</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>27/4/2026, 2:03:14 pm</v>
+      </c>
+      <c r="C92" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D92" t="str">
+        <v>Java Architect</v>
+      </c>
+      <c r="E92" t="str">
+        <v>Valuelabs</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Hyderabad(HITEC City)</v>
+      </c>
+      <c r="G92" t="str">
+        <v>https://www.naukri.com/job-listings-java-architect-valuelabs-hyderabad-9-to-14-years-270426907963</v>
+      </c>
+      <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>27/4/2026, 2:04:25 pm</v>
+      </c>
+      <c r="C93" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D93" t="str">
+        <v>Senior Full Stack Developer</v>
+      </c>
+      <c r="E93" t="str">
+        <v>Soothsayer Analytics</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G93" t="str">
+        <v>https://www.naukri.com/job-listings-senior-full-stack-developer-soothsayer-analytics-hyderabad-8-to-10-years-240426924339</v>
+      </c>
+      <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>27/4/2026, 2:05:31 pm</v>
+      </c>
+      <c r="C94" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D94" t="str">
+        <v>Senior Software Engineer</v>
+      </c>
+      <c r="E94" t="str">
+        <v>S&amp;P Global Market Intelligence</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G94" t="str">
+        <v>https://www.naukri.com/job-listings-senior-software-engineer-sp-capital-iq-india-pvt-ltd-hyderabad-6-to-11-years-210426935525</v>
+      </c>
+      <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>27/4/2026, 2:05:47 pm</v>
+      </c>
+      <c r="C95" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D95" t="str">
+        <v>Lead UI Developer- React, Node.js</v>
+      </c>
+      <c r="E95" t="str">
+        <v>S&amp;P Global Market Intelligence</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Hyderabad, Noida</v>
+      </c>
+      <c r="G95" t="str">
+        <v>https://www.naukri.com/job-listings-lead-ui-developer-react-node-js-sp-capital-iq-india-pvt-ltd-noida-hyderabad-4-to-6-years-210426911420</v>
+      </c>
+      <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>27/4/2026, 2:05:55 pm</v>
+      </c>
+      <c r="C96" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D96" t="str">
+        <v>Senior Associate Software Engineering(.Net)</v>
+      </c>
+      <c r="E96" t="str">
+        <v>EMBARK SERVICES PRIVATE LIMITED</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G96" t="str">
+        <v>https://www.naukri.com/job-listings-senior-associate-software-engineering-net-embark-services-private-limited-hyderabad-5-to-7-years-210426012200</v>
+      </c>
+      <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>27/4/2026, 2:06:03 pm</v>
+      </c>
+      <c r="C97" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D97" t="str">
+        <v>Full Stack Developer | Java / Python &amp; React / Node</v>
+      </c>
+      <c r="E97" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G97" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-java-python-react-node-cerebra-hyderabad-8-to-11-years-240426028799</v>
+      </c>
+      <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>27/4/2026, 2:06:11 pm</v>
+      </c>
+      <c r="C98" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D98" t="str">
+        <v>Fullstack Software Developer</v>
+      </c>
+      <c r="E98" t="str">
+        <v>ARi Global</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G98" t="str">
+        <v>https://www.naukri.com/job-listings-fullstack-software-developer-ari-global-hyderabad-6-to-8-years-240426022488</v>
+      </c>
+      <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
+        <v>unknown_state</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>27/4/2026, 2:06:19 pm</v>
+      </c>
+      <c r="C99" t="str">
+        <v>naukri</v>
+      </c>
+      <c r="D99" t="str">
+        <v>Full Stack Developer | Java/Python &amp; React/Node</v>
+      </c>
+      <c r="E99" t="str">
+        <v>Cerebra</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="G99" t="str">
+        <v>https://www.naukri.com/job-listings-full-stack-developer-java-python-react-node-cerebra-hyderabad-8-to-10-years-230426014905</v>
+      </c>
+      <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
+        <v>unknown_state</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I99"/>
   </ignoredErrors>
 </worksheet>
 </file>